--- a/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
+++ b/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
@@ -48,7 +48,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'양식목록'!$8:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'양식목록'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'양식목록'!$A$1:$F$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'문서관리'!$A$1:$E$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'작성안내'!$A$1:$B$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PF-00'!$A$1:$G$29</definedName>
@@ -71,10 +71,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="14">'QF-11'!$A$1:$K$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'QF-12'!$12:$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'QF-12'!$A$1:$K$44</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'QF-13'!$12:$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'QF-13'!$A$1:$I$47</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'QF-13'!$13:$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'QF-13'!$A$1:$I$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="17">'QF-13-2'!$11:$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'QF-13-2'!$A$1:$G$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'QF-13-2'!$A$1:$G$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="18">'QF-14'!$10:$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'QF-14'!$A$1:$J$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="19">'QF-15'!$14:$14</definedName>
@@ -84,12 +84,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="21">'SF-01'!$A$1:$M$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'SF-02'!$A$1:$E$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'SF-03'!$A$1:$F$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="24">'SF-04'!$A$1:$H$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="25">'SF-05'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'SF-04'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'SF-05'!$A$1:$H$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="26">'SF-06'!$13:$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="26">'SF-06'!$A$1:$H$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="27">'SF-07'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="28">'SF-08'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'SF-08'!$A$1:$H$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="29">'SF-09'!$A$1:$H$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="30">'SF-10'!$A$1:$H$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="31">'EF-01'!$12:$12</definedName>
@@ -97,10 +97,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="32">'MF-01'!$13:$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="32">'MF-01'!$A$1:$G$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="33">'MF-02'!$A$1:$F$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="34">'MF-03'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'MF-03'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="35">'MF-04'!$A$1:$G$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="36">'MF-05'!$11:$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'MF-05'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'MF-05'!$A$1:$H$56</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="37">'MF-06'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1801,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F49"/>
+  <dimension ref="A2:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>주 1회 백업 확인 / 월 1회 표본 복구</t>
+          <t>분기 1회 표본 복구 / 백업 실패 시</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>안전보건관리담당자 선임 및 직무 평가</t>
+          <t>안전보건관리담당자·관리감독자 지정 및 반기 평가</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="31.65" customHeight="1">
+    <row r="31" ht="44.475" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>SF-05</t>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>매년 1월 계획 / 교육 실시 시 / 반기 실적 확인</t>
+          <t>매년 1월 계획 / 교육 실시 시 / 반기 실적은 SF-08 점검 때</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="31.65" customHeight="1">
+    <row r="33" ht="44.475" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>SF-07</t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>매년 1월 편성 / 분기 집행 확인 / 추가 필요 시</t>
+          <t>매년 1월 편성 / 반기 집행 확인 (SF-08 때) / 추가 필요 시</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>연초·분기 실적·경영검토</t>
+          <t>연초 계획·반기 실적 (6·12월)·경영검토</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="31.65" customHeight="1">
+    <row r="42" ht="44.475" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>MF-05</t>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>최초·변경 시·분기 최신성 확인·연 1회 평가</t>
+          <t>최초·변경 시·반기 최신성 확인 (SF-08 때)·연 1회 평가</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>월 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
+          <t>분기 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -3054,14 +3054,6 @@
       <c r="D48" s="5" t="n"/>
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7457,7 +7449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:I47"/>
+  <dimension ref="A2:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.7" customWidth="1" min="1" max="1"/>
@@ -7575,7 +7567,7 @@
     <row r="10" ht="14.15" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>백업 성공 확인과 월별 표본 복구는 QF-13-2에 기록한다.</t>
+          <t>분기 표본 복구와 백업 실패 조치는 QF-13-2에 기록한다.</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -7587,86 +7579,78 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
     </row>
-    <row r="11" ht="5" customHeight="1"/>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="11" ht="14.15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>외부 문서(고객 사양서·적용 규격·제조사 자료)는 받은 판본을 확인해 프로젝트 02_설계기준에 두고, 회사 공통으로 쓰는 외부 문서만 아래에 판본을 등록한다.</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="5" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>문서·기록번호</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>명칭·종류</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>승인자·승인일</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>시행일</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>배포처·회수</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>보관 경로</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>보존 기산·기간</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>DI-IMS-M-01</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>통합경영 매뉴얼</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>DI-IMS-F-01</t>
+          <t>DI-IMS-M-01</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>통합 기록양식집</t>
+          <t>통합경영 매뉴얼</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -7681,15 +7665,15 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
     </row>
-    <row r="15" ht="31.65" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>WI-01</t>
+          <t>DI-IMS-F-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>판넬 내부 배선 작업 기준 (매뉴얼 부록 B)</t>
+          <t>통합 기록양식집</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -7704,10 +7688,22 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
+    <row r="16" ht="31.65" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>WI-01</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>판넬 내부 배선 작업 기준 (매뉴얼 부록 B)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
@@ -7715,10 +7711,22 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+    <row r="17" ht="44.475" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>외부 문서</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>공통 외부 문서 (적용 규격·주요 부품 제조사 매뉴얼) — 판본 확인</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>수령본</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
@@ -8001,50 +8009,54 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>작성</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="13" t="n"/>
       <c r="B45" s="13" t="n"/>
       <c r="C45" s="13" t="n"/>
       <c r="D45" s="13" t="n"/>
       <c r="E45" s="13" t="n"/>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>작성</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>성명·서명</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="13" t="n"/>
       <c r="B46" s="13" t="n"/>
       <c r="C46" s="13" t="n"/>
@@ -8052,31 +8064,17 @@
       <c r="E46" s="13" t="n"/>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>성명·서명</t>
+          <t>일자</t>
         </is>
       </c>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="10" t="n"/>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="13" t="n"/>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="G5:I5"/>
@@ -8084,7 +8082,7 @@
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A45:E47"/>
+    <mergeCell ref="A44:E46"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="A6:B6"/>
@@ -8110,7 +8108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G75"/>
+  <dimension ref="A2:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.3" customWidth="1" min="1" max="1"/>
@@ -8139,7 +8137,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-QF-13-2 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 경영관리 / 품질 | 작성: 주 1회 백업 확인 / 월 1회 표본 복구</t>
+          <t>동인엔시스 | DI-QF-13-2 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 경영관리 / 품질 | 작성: 분기 1회 표본 복구 / 백업 실패 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -8185,10 +8183,10 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7" ht="5" customHeight="1"/>
-    <row r="8" ht="14.15" customHeight="1">
+    <row r="8" ht="26.3" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>백업은 작업일마다 실행하고, 주 1회 성공 여부를, 월 1회 표본 복구(도면·PLC·검사기록 각 1건 이상)를 확인한다.</t>
+          <t>백업은 NAS 등에서 자동으로 매일 실행되게 설정하고 실패 알림을 받는다(성공 여부를 따로 적지 않는다). 분기 1회(3·6·9·12월) 도면·PLC·검사기록 각 1건 이상을 실제로 복구해 열어 보고 기록한다.</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -8357,493 +8355,61 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="14" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="14" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="14" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="14" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="14" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="14" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="14" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="14" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="14" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="14" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="14" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="14" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="14" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="14" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="14" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="14" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="14" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="14" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="14" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="14" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="14" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="14" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="14" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="14" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="14" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-    </row>
-    <row r="72" ht="6" customHeight="1"/>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="13" t="n"/>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="13" t="n"/>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="9" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>성명·서명</t>
         </is>
       </c>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="13" t="n"/>
-      <c r="B75" s="13" t="n"/>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -8854,24 +8420,24 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A73:C75"/>
+    <mergeCell ref="A25:C27"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
-  <conditionalFormatting sqref="B12:B71">
+  <conditionalFormatting sqref="B12:B23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>OR(B12="불합격",B12="보류",B12="부적합",B12="미흡",B12="미준수",B12="미확인",B12="실패",B12="사용금지",B12="중지·개선",B12="재교육·동행",B12="C 발주중지",B12="중요")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D71">
+  <conditionalFormatting sqref="D12:D23">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>OR(D12="불합격",D12="보류",D12="부적합",D12="미흡",D12="미준수",D12="미확인",D12="실패",D12="사용금지",D12="중지·개선",D12="재교육·동행",D12="C 발주중지",D12="중요")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B12:B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 주간 백업 확인, 월간 표본 복구, 실패 조치" type="list" errorStyle="warning">
-      <formula1>"주간 백업 확인,월간 표본 복구,실패 조치"</formula1>
+    <dataValidation sqref="B12:B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 분기 표본 복구, 백업 실패·조치" type="list" errorStyle="warning">
+      <formula1>"분기 표본 복구,백업 실패·조치"</formula1>
     </dataValidation>
-    <dataValidation sqref="D12:D71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 성공, 실패" type="list" errorStyle="warning">
+    <dataValidation sqref="D12:D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 성공, 실패" type="list" errorStyle="warning">
       <formula1>"성공,실패"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9381,12 +8947,28 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
+    <row r="9" ht="82.95" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>00 (보완)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026.10.12</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>법정·인증 필수 정리: SF-04에 관리감독자 지정·반기 평가, MF-05에 관리감독자·휴게시설·법정 의무교육·인원 기준, SF-05에 성희롱 예방·장애인 인식개선 교육, QF-13 외부 문서 추가 / 근로자 협의·표본 복구 분기, 목표 실적·법규 최신성·예산 집행 확인 반기(SF-08 때)로 조정</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>대표 승인 후 적용</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5" t="n"/>
@@ -12451,7 +12033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H25"/>
+  <dimension ref="A2:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.7" customWidth="1" min="1" max="1"/>
@@ -12468,7 +12050,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>안전보건관리담당자 선임 및 직무 평가</t>
+          <t>안전보건관리담당자·관리감독자 지정 및 반기 평가</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -12562,25 +12144,25 @@
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="10" t="n"/>
     </row>
-    <row r="9" ht="5" customHeight="1"/>
-    <row r="10" ht="14.15" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>선임 근거: 산업안전보건법 제19조(상시근로자 20~49명 제조업). 선임 증빙은 이 양식과 첨부로 보관한다. 보수교육은 시행규칙 별표4 기준 8시간 이상이며 주기는 MF-05에서 확인한다.</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="14.15" customHeight="1">
+    <row r="9" ht="28.3" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>관리감독자 (성명 / 지휘하는 작업) — 지정일</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="5" customHeight="1"/>
+    <row r="11" ht="26.3" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>부여 권한: 급박위험 시 작업중지 / SF-07 예산 집행 요청 / 외주 작업 중지 요청. 반기마다 대표가 직무 수행을 평가하고 결과를 SF-08에 연결한다. 미흡은 개선 계획과 기한을 정한다.</t>
+          <t>관리감독자: 생산·시험 등 작업을 직접 지휘하는 사람을 대표가 지정한다(산업안전보건법 제16조). 중대재해처벌법 시행령 제4조 제5호에 따라 안전보건관리담당자와 함께 반기마다 평가한다. 아래 '관리감독자' 행은 지정된 사람마다 평가한다.</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -12591,94 +12173,86 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
     </row>
-    <row r="12" ht="5" customHeight="1"/>
-    <row r="13" ht="31.65" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="12" ht="14.15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>선임 근거: 산업안전보건법 제19조(상시근로자 20~49명 제조업). 선임 증빙은 이 양식과 첨부로 보관한다. 보수교육은 시행규칙 별표4 기준 8시간 이상이며 주기는 MF-05에서 확인한다.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="14.15" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>부여 권한: 급박위험 시 작업중지 / SF-07 예산 집행 요청 / 외주 작업 중지 요청. 반기마다 대표가 직무 수행을 평가하고 결과를 SF-08에 연결한다. 미흡은 개선 계획과 기한을 정한다.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="5" customHeight="1"/>
+    <row r="15" ht="31.65" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>직무</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>수행 기준</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>상반기 실적·증거</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>상반기 평가</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>하반기 실적·증거</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>하반기 평가</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>미흡·개선 조치</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>대표 확인</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="31.65" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>위험성평가 실시·조치 지도 (SF-01)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>최초·연 1회·수시 평가, 대책 이행 확인</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="31.65" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>안전보건교육 계획·실시 (SF-05)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>연간 계획, 반기 이수율 100%</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="31.65" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>건강진단·작업환경 확인 (SF-06)</t>
+          <t>위험성평가 실시·조치 지도 (SF-01)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>대상자 수검, 유해인자 판정</t>
+          <t>최초·연 1회·수시 평가, 대책 이행 확인</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -12691,12 +12265,12 @@
     <row r="17" ht="31.65" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>산업재해 원인조사·재발방지 (SF-10)</t>
+          <t>안전보건교육 계획·실시 (SF-05)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>발생 시 조사·대책·SF-01 재검토</t>
+          <t>연간 계획, 반기 이수율 100%</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -12706,15 +12280,15 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="31.65" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>보호구 선정·지급·착용 지도</t>
+          <t>건강진단·작업환경 확인 (SF-06)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>작업별 지급 기록, 착용 점검</t>
+          <t>대상자 수검, 유해인자 판정</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -12727,12 +12301,12 @@
     <row r="19" ht="31.65" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>외주 작업 안전 협의·순회 (SF-03·SF-09)</t>
+          <t>산업재해 원인조사·재발방지 (SF-10)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>작업 전 협의, 순회 확인 기록</t>
+          <t>발생 시 조사·대책·SF-01 재검토</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -12745,12 +12319,12 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>법규 준수 확인 (MF-05)</t>
+          <t>보호구 선정·지급·착용 지도</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>분기 최신성 확인, 연 1회 준수평가</t>
+          <t>작업별 지급 기록, 착용 점검</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -12763,12 +12337,12 @@
     <row r="21" ht="31.65" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>근로자 의견 청취·회신 (MF-06)</t>
+          <t>외주 작업 안전 협의·순회 (SF-03·SF-09)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>월 1회 협의, 회신 기한 준수</t>
+          <t>작업 전 협의, 순회 확인 기록</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -12778,101 +12352,193 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>법규 준수 확인 (MF-05)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>반기 최신성 확인, 연 1회 준수평가</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="31.65" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>근로자 의견 청취·회신 (MF-06)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>분기 1회 협의, 회신 기한 준수</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="31.65" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>관리감독자: 작업 전 점검</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>기계·기구·전기설비 작업 전 점검, 이상 시 사용중지</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>관리감독자: 작업 지도</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>보호구 착용·작업 방법 지도, 정리정돈</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="31.65" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>관리감독자: 재해 대응·위험성평가</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>재해 시 보고·응급조치, SF-01 참여</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>대표이사</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>성명·서명</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="13" t="n"/>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C24:D24"/>
+  <mergeCells count="20">
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A28:B30"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A23:B25"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A13:H13"/>
   </mergeCells>
-  <conditionalFormatting sqref="D14:D21">
+  <conditionalFormatting sqref="D16:D26">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(D14="불합격",D14="보류",D14="부적합",D14="미흡",D14="미준수",D14="미확인",D14="실패",D14="사용금지",D14="중지·개선",D14="재교육·동행",D14="C 발주중지",D14="중요")</formula>
+      <formula>OR(D16="불합격",D16="보류",D16="부적합",D16="미흡",D16="미준수",D16="미확인",D16="실패",D16="사용금지",D16="중지·개선",D16="재교육·동행",D16="C 발주중지",D16="중요")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F21">
+  <conditionalFormatting sqref="F16:F26">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>OR(F14="불합격",F14="보류",F14="부적합",F14="미흡",F14="미준수",F14="미확인",F14="실패",F14="사용금지",F14="중지·개선",F14="재교육·동행",F14="C 발주중지",F14="중요")</formula>
+      <formula>OR(F16="불합격",F16="보류",F16="부적합",F16="미흡",F16="미준수",F16="미확인",F16="실패",F16="사용금지",F16="중지·개선",F16="재교육·동행",F16="C 발주중지",F16="중요")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="D14:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
+    <dataValidation sqref="D16:D26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
       <formula1>"적합,부분,미흡"</formula1>
     </dataValidation>
-    <dataValidation sqref="F14:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
+    <dataValidation sqref="F16:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
       <formula1>"적합,부분,미흡"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12897,7 +12563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H27"/>
+  <dimension ref="A2:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.7" customWidth="1" min="1" max="1"/>
@@ -12928,7 +12594,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 경영관리 | 작성: 매년 1월 계획 / 교육 실시 시 / 반기 실적 확인</t>
+          <t>동인엔시스 | DI-SF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리 / 경영관리 | 작성: 매년 1월 계획 / 교육 실시 시 / 반기 실적은 SF-08 점검 때</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -13278,85 +12944,129 @@
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
+    <row r="23" ht="31.65" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>직장 내 성희롱 예방교육 (남녀고용평등법 제13조)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>전 직원 (대표 포함)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>연 1회 이상</t>
+        </is>
+      </c>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="24" ht="31.65" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>장애인 인식개선 교육 (장애인고용촉진법 제5조의2)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>전 직원</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>연 1회 이상</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>작성</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="n"/>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>성명·서명</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="13" t="n"/>
       <c r="B27" s="13" t="n"/>
       <c r="C27" s="13" t="n"/>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>작성</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>성명·서명</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A25:D27"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A27:D29"/>
     <mergeCell ref="E5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -14006,10 +13716,10 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="26.3" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-SF-07 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표이사 / 왕리홍 대리 / 경영관리 | 작성: 매년 1월 편성 / 분기 집행 확인 / 추가 필요 시</t>
+          <t>동인엔시스 | DI-SF-07 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표이사 / 왕리홍 대리 / 경영관리 | 작성: 매년 1월 편성 / 반기 집행 확인 (SF-08 때) / 추가 필요 시</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -14042,7 +13752,7 @@
     <row r="6" ht="28.3" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>분기 집행 확인일 (3·6·9·12월) / 확인자</t>
+          <t>반기 집행 확인일 (6·12월, SF-08) / 확인자</t>
         </is>
       </c>
       <c r="B6" s="10" t="n"/>
@@ -14382,7 +14092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H25"/>
+  <dimension ref="A2:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.6" customWidth="1" min="1" max="1"/>
@@ -14478,7 +14188,7 @@
     <row r="8" ht="40.45" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>기계·기구(사용 시): 크레인·호이스트·지게차 검사·점검·운전자격 / 전기설비 접지·누전차단기</t>
+          <t>휴게시설 (산업안전보건법 제128조의2, 20명 이상): 설치·면적·온도·조명·환기·관리담당</t>
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
@@ -14489,91 +14199,87 @@
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="10" t="n"/>
     </row>
-    <row r="9" ht="5" customHeight="1"/>
-    <row r="10" ht="26.3" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="9" ht="40.45" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>기계·기구(사용 시): 크레인·호이스트·지게차 검사·점검·운전자격 / 전기설비 접지·누전차단기</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="5" customHeight="1"/>
+    <row r="11" ht="26.3" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>중대재해처벌법 시행령 제4조·제5조의 이행 항목을 반기마다 점검하여 대표에게 보고한다. 판정(적합/부분/미흡)에는 근거 기록 번호를 함께 적는다. 미흡은 QF-09로 조치하고 SF-07 예산에 반영한다.</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="5" customHeight="1"/>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="5" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>점검 항목</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>확인 기준</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>근거 기록</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>미흡 내용</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>조치·담당</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>기한</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>완료 확인</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>안전보건 방침·목표 (MF-03)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>방침 게시·공유, 목표 실적 확인</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="31.65" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>유해·위험요인 확인·개선 (SF-01)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>반기 점검, 6~9 위험 개선 완료</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -14586,12 +14292,12 @@
     <row r="15" ht="31.65" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>안전보건 예산 편성·집행 (SF-07)</t>
+          <t>유해·위험요인 확인·개선 (SF-01)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>용도대로 집행, 미집행 사유</t>
+          <t>반기 점검, 6~9 위험 개선 완료</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -14604,12 +14310,12 @@
     <row r="16" ht="31.65" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>관리담당자 선임·직무 평가 (SF-04)</t>
+          <t>안전보건 예산 편성·집행 (SF-07)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>선임 유효, 반기 평가 실시</t>
+          <t>용도대로 집행, 미집행 사유</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -14622,12 +14328,12 @@
     <row r="17" ht="31.65" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>종사자 의견 청취·조치 (MF-06)</t>
+          <t>관리담당자·관리감독자 지정·평가 (SF-04)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>월 1회 협의, 조치 회신</t>
+          <t>선임·지정 유효, 반기 평가 실시</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -14640,12 +14346,12 @@
     <row r="18" ht="31.65" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>재해 대응 절차·비상훈련 (SF-10·MF-06)</t>
+          <t>종사자 의견 청취·조치 (MF-06)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>대응 절차 게시, 연 1회 훈련</t>
+          <t>분기 1회 협의, 조치 회신</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -14658,12 +14364,12 @@
     <row r="19" ht="31.65" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>외주 안전보건 확보 (SF-09·SF-03)</t>
+          <t>재해 대응 절차·비상훈련 (SF-10·MF-06)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>선정 전 평가, 작업 전 협의</t>
+          <t>대응 절차 게시, 연 1회 훈련</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -14676,12 +14382,12 @@
     <row r="20" ht="31.65" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>교육·건강진단 (SF-05·SF-06)</t>
+          <t>외주 안전보건 확보 (SF-09·SF-03)</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>반기 이수율, 수검 현황</t>
+          <t>선정 전 평가, 작업 전 협의</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -14694,12 +14400,12 @@
     <row r="21" ht="31.65" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>안전·보건 관계 법령 이행 (MF-05)</t>
+          <t>교육·건강진단 (SF-05·SF-06)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>의무별 준수 상태, 미준수 조치</t>
+          <t>반기 이수율·미이수 보충, 수검 현황</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -14709,84 +14415,121 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>목표 반기 실적 (MF-03)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>지표 실적·미달 조치</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="31.65" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>안전·보건 관계 법령 이행 (MF-05)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>의무별 준수 상태, 미준수 조치</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>작성</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>성명·서명</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>작성</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>성명·서명</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A25:D27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A10:H10"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A23:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="D13:D21">
+  <conditionalFormatting sqref="D14:D23">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(D13="불합격",D13="보류",D13="부적합",D13="미흡",D13="미준수",D13="미확인",D13="실패",D13="사용금지",D13="중지·개선",D13="재교육·동행",D13="C 발주중지",D13="중요")</formula>
+      <formula>OR(D14="불합격",D14="보류",D14="부적합",D14="미흡",D14="미준수",D14="미확인",D14="실패",D14="사용금지",D14="중지·개선",D14="재교육·동행",D14="C 발주중지",D14="중요")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D13:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
+    <dataValidation sqref="D14:D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 적합, 부분, 미흡" type="list" errorStyle="warning">
       <formula1>"적합,부분,미흡"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14964,7 +14707,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>필수 시점: 프로젝트 단계별 기록 / 통전 시작·상태변경·종료 SF-02 / 월별 협의(MF-06)·복구확인(QF-13-2) / 분기 목표실적·법규최신성 / 연간 내부심사·경영검토·위험/환경 재평가·비상훈련·공급자 재평가 / 연초 SF-05·SF-06·SF-07 계획 / 6월·12월 SF-08 반기 점검 및 SF-04 평가 / 재해 발생 즉시 SF-10</t>
+          <t>필수 시점: 프로젝트 단계별 기록 / 통전 시작·상태변경·종료 SF-02 / 분기 협의(MF-06)·표본 복구(QF-13-2) / 6월·12월 SF-08 반기 점검 때 SF-04 평가·목표 실적·법규 최신성·예산·교육 실적 / 연간 내부심사·경영검토·위험/환경 재평가·비상훈련·공급자 재평가 / 연초 SF-05·SF-06·SF-07 계획 / 재해 발생 즉시 SF-10</t>
         </is>
       </c>
     </row>
@@ -17919,7 +17662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J21"/>
+  <dimension ref="A2:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.7" customWidth="1" min="1" max="1"/>
@@ -17927,11 +17670,9 @@
     <col width="12.6" customWidth="1" min="3" max="3"/>
     <col width="21.1" customWidth="1" min="4" max="4"/>
     <col width="9.5" customWidth="1" min="5" max="5"/>
-    <col width="9.5" customWidth="1" min="6" max="6"/>
-    <col width="9.5" customWidth="1" min="7" max="7"/>
-    <col width="9.5" customWidth="1" min="8" max="8"/>
-    <col width="9.5" customWidth="1" min="9" max="9"/>
-    <col width="16.8" customWidth="1" min="10" max="10"/>
+    <col width="14.7" customWidth="1" min="6" max="6"/>
+    <col width="14.7" customWidth="1" min="7" max="7"/>
+    <col width="25.3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1"/>
@@ -17948,13 +17689,11 @@
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-03 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표 / 각 담당 | 작성: 연초·분기 실적·경영검토</t>
+          <t>동인엔시스 | DI-MF-03 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 대표 / 각 담당 | 작성: 연초 계획·반기 실적 (6·12월)·경영검토</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -17964,8 +17703,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="20" customHeight="1">
@@ -17977,22 +17714,20 @@
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>승인자·일자</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="n"/>
     </row>
     <row r="6" ht="5" customHeight="1"/>
     <row r="7" ht="14.15" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>고객·법규·중요측면·위험 결과와 연결한다. 사내 목표값은 대표 승인 후 유효하다. 분기 실적과 증거를 적고, 사고 0건만으로 안전성과를 평가하지 않고 고위험 개선 이행 등 선행지표도 본다.</t>
+          <t>고객·법규·중요측면·위험 결과와 연결한다. 사내 목표값은 대표 승인 후 유효하다. 반기 실적과 증거를 적고, 사고 0건만으로 안전성과를 평가하지 않고 고위험 개선 이행 등 선행지표도 본다.</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -18002,8 +17737,6 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
     </row>
     <row r="8" ht="5" customHeight="1"/>
     <row r="9" ht="26" customHeight="1">
@@ -18034,25 +17767,15 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1분기</t>
+          <t>상반기 실적</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2분기</t>
+          <t>하반기 실적</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3분기</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>4분기</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>평가·미달조치</t>
         </is>
@@ -18075,8 +17798,6 @@
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11" ht="31.65" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -18095,8 +17816,6 @@
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
     </row>
     <row r="12" ht="31.65" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -18115,8 +17834,6 @@
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -18135,8 +17852,6 @@
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -18155,8 +17870,6 @@
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
     </row>
     <row r="15" ht="31.65" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -18175,8 +17888,6 @@
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="n"/>
@@ -18187,8 +17898,6 @@
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="5" t="n"/>
@@ -18199,8 +17908,6 @@
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18" ht="6" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
@@ -18222,14 +17929,12 @@
           <t>작성</t>
         </is>
       </c>
-      <c r="G19" s="8" t="n"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
       <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
@@ -18248,8 +17953,6 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="13" t="n"/>
@@ -18264,26 +17967,17 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="9">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:H7"/>
     <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="A19:C21"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G5:J5"/>
     <mergeCell ref="D21:E21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -18693,7 +18387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H39"/>
+  <dimension ref="A2:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.4" customWidth="1" min="1" max="1"/>
@@ -18721,10 +18415,10 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="26.3" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리·성문기 과장 / 품질 | 작성: 최초·변경 시·분기 최신성 확인·연 1회 평가</t>
+          <t>동인엔시스 | DI-MF-05 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 왕리홍 대리·성문기 과장 / 품질 | 작성: 최초·변경 시·반기 최신성 확인 (SF-08 때)·연 1회 평가</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -18897,12 +18591,12 @@
     <row r="15" ht="31.65" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제19조</t>
+          <t>산업안전보건법 제16조</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>안전보건관리담당자 선임·증빙 (상시 20~49명 제조업)</t>
+          <t>관리감독자 지정·업무 (작업 지휘자) — SF-04 반기 평가</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -18915,12 +18609,12 @@
     <row r="16" ht="31.65" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제29조·제32조</t>
+          <t>산업안전보건법 제19조</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>근로자 정기·채용·작업변경·특별교육 / 관리담당자 보수교육</t>
+          <t>안전보건관리담당자 선임·증빙 (상시 20~49명 제조업)</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -18933,12 +18627,12 @@
     <row r="17" ht="31.65" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제34조·제37조</t>
+          <t>산업안전보건법 제29조·제32조</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>법령 요지 게시 / 안전보건표지</t>
+          <t>근로자 정기·채용·작업변경·특별교육 / 관리담당자 보수교육</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -18951,12 +18645,12 @@
     <row r="18" ht="31.65" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제36조</t>
+          <t>산업안전보건법 제34조·제37조</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>위험성평가 실시·근로자 참여·결과 공유·기록 3년 보존</t>
+          <t>법령 요지 게시 / 안전보건표지</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -18969,12 +18663,12 @@
     <row r="19" ht="31.65" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제38조, 안전보건규칙 전기작업</t>
+          <t>산업안전보건법 제36조</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>정전전로·충전전로 작업 조치, 누전차단기·접지</t>
+          <t>위험성평가 실시·근로자 참여·결과 공유·기록 3년 보존</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -18987,12 +18681,12 @@
     <row r="20" ht="31.65" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제54조·제57조</t>
+          <t>산업안전보건법 제38조, 안전보건규칙 전기작업</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>중대재해 보고 / 산업재해조사표 1개월 이내 제출·3년 보존</t>
+          <t>정전전로·충전전로 작업 조치, 누전차단기·접지</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -19005,12 +18699,12 @@
     <row r="21" ht="31.65" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제63조·제64조</t>
+          <t>산업안전보건법 제54조·제57조</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>도급인 안전조치, 수급인 작업 협의·순회점검</t>
+          <t>중대재해 보고 / 산업재해조사표 1개월 이내 제출·3년 보존</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -19023,12 +18717,12 @@
     <row r="22" ht="31.65" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제93조 등</t>
+          <t>산업안전보건법 제63조·제64조</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>크레인·호이스트 안전검사, 지게차 점검·운전자격</t>
+          <t>도급인 안전조치, 수급인 작업 협의·순회점검</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -19041,12 +18735,12 @@
     <row r="23" ht="31.65" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제114조</t>
+          <t>산업안전보건법 제93조 등</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>MSDS 비치·게시·교육·경고표시 (세척제·도료 등)</t>
+          <t>크레인·호이스트 안전검사, 지게차 점검·운전자격</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -19059,12 +18753,12 @@
     <row r="24" ht="31.65" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>산업안전보건법 제125조·제129조·제130조</t>
+          <t>산업안전보건법 제114조</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>작업환경측정·일반/특수건강진단</t>
+          <t>MSDS 비치·게시·교육·경고표시 (세척제·도료 등)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -19077,12 +18771,12 @@
     <row r="25" ht="31.65" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>중대재해처벌법 제4조, 시행령 제4조·제5조</t>
+          <t>산업안전보건법 제125조·제129조·제130조</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>안전보건관리체계 구축·반기 점검·대표 보고</t>
+          <t>작업환경측정·일반/특수건강진단</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -19095,12 +18789,12 @@
     <row r="26" ht="31.65" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>폐기물관리법</t>
+          <t>산업안전보건법 제128조의2</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>사업장폐기물 분리·보관·위탁처리·인계 증빙</t>
+          <t>휴게시설 설치·관리기준 (상시 20명 이상) — SF-08 반기 확인</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -19110,15 +18804,15 @@
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="31.65" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>화학물질 관계 법령</t>
+          <t>중대재해처벌법 제4조, 시행령 제4조·제5조</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>취급물질 해당 여부·표시·보관</t>
+          <t>안전보건관리체계 구축·반기 점검·대표 보고</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -19131,12 +18825,12 @@
     <row r="28" ht="31.65" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>소방 관계 법령</t>
+          <t>폐기물관리법</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>소화설비·자체점검·소방안전관리자 해당 여부</t>
+          <t>사업장폐기물 분리·보관·위탁처리·인계 증빙</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -19146,15 +18840,15 @@
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="5" t="n"/>
     </row>
-    <row r="29" ht="31.65" customHeight="1">
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>전기안전관리법</t>
+          <t>화학물질 관계 법령</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>자가용 전기설비 전기안전관리자 선임(대행) 해당 여부</t>
+          <t>취급물질 해당 여부·표시·보관</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -19167,12 +18861,12 @@
     <row r="30" ht="31.65" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>대기환경보전법</t>
+          <t>소방 관계 법령</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>도장·용접 등 배출시설 해당 여부 (외주 시 해당없음 근거)</t>
+          <t>소화설비·자체점검·소방안전관리자 해당 여부</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -19182,9 +18876,17 @@
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="5" t="n"/>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
+    <row r="31" ht="31.65" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>전기안전관리법</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>자가용 전기설비 전기안전관리자 선임(대행) 해당 여부</t>
+        </is>
+      </c>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
@@ -19192,9 +18894,17 @@
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="5" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
+    <row r="32" ht="31.65" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>대기환경보전법</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>도장·용접 등 배출시설 해당 여부 (외주 시 해당없음 근거)</t>
+        </is>
+      </c>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
@@ -19202,9 +18912,17 @@
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="5" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
+    <row r="33" ht="31.65" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>남녀고용평등법 제13조 · 장애인고용촉진법 제5조의2</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>성희롱 예방교육·장애인 인식개선 교육 연 1회 (SF-05)</t>
+        </is>
+      </c>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
@@ -19212,9 +18930,17 @@
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="5" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
+    <row r="34" ht="44.475" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>인원 기준 변동 (상시 30명·50명)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>30명 이상 노사협의회 / 50명 이상 안전보건관리책임자·안전·보건관리자·산업안전보건위원회 — 인원 변동 시 재확인</t>
+        </is>
+      </c>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
@@ -19232,64 +18958,234 @@
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="5" t="n"/>
     </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="13" t="n"/>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="9" t="inlineStr">
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>성명·서명</t>
         </is>
       </c>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -19298,17 +19194,17 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="A37:D39"/>
+    <mergeCell ref="A54:D56"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="E5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G12:G35">
+  <conditionalFormatting sqref="G12:G52">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>OR(G12="불합격",G12="보류",G12="부적합",G12="미흡",G12="미준수",G12="미확인",G12="실패",G12="사용금지",G12="중지·개선",G12="재교육·동행",G12="C 발주중지",G12="중요")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G12:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 준수, 미준수, 미확인, 해당없음" type="list" errorStyle="warning">
+    <dataValidation sqref="G12:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 준수, 미준수, 미확인, 해당없음" type="list" errorStyle="warning">
       <formula1>"준수,미준수,미확인,해당없음"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19360,7 +19256,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>동인엔시스 | DI-MF-06 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 안전·환경 담당 | 작성: 월 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
+          <t>동인엔시스 | DI-MF-06 | Rev.00 | 제정 2026.10.01 | 시행 2026.10.01 (대표 승인)   ·   담당: 안전·환경 담당 | 작성: 분기 1회 협의 / 연 1회 훈련 / 변경·실제 비상 후</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -19446,7 +19342,7 @@
     <row r="11" ht="26.3" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>기존 회의록이 이 필드를 모두 포함하면 대체 가능하다. 화재·감전·누출 등 실제 위험에 맞는 시나리오로 신고·대피·전원차단·응급연락을 연습하며 결과로 계획을 수정한다. 참석 서명은 QF-12 서명란 또는 기존 서명부를 첨부한다.</t>
+          <t>협의는 분기 1회(3·6·9·12월) 기존 회의에 안전 안건으로 넣어도 된다. 근로자는 그 밖에도 언제든 의견을 낼 수 있다. 기존 회의록이 이 필드를 모두 포함하면 대체 가능하다. 화재·감전·누출 등 실제 위험에 맞는 시나리오로 신고·대피·전원차단·응급연락을 연습하며 결과로 계획을 수정한다. 참석 서명은 QF-12 서명란 또는 기존 서명부를 첨부한다.</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -19628,8 +19524,8 @@
     <mergeCell ref="E9:F9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 월 협의, 비상훈련, 실제 비상 대응 검토" type="list" errorStyle="warning">
-      <formula1>"월 협의,비상훈련,실제 비상 대응 검토"</formula1>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 분기 협의, 비상훈련, 실제 비상 대응 검토" type="list" errorStyle="warning">
+      <formula1>"분기 협의,비상훈련,실제 비상 대응 검토"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -19996,7 +19892,7 @@
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
     </row>
-    <row r="24" ht="31.65" customHeight="1">
+    <row r="24" ht="44.475" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>종료</t>
@@ -20004,7 +19900,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>최종 도면·PLC 백업 · 납품자료 · 고객재산 반환 · 보증 개시일 확정</t>
+          <t>최종 도면·PLC 백업 · 납품자료 · 고객재산 반환 · 보증 개시일 확정 · 배운 점 한 줄(표준 도면·PLC 라이브러리 반영 여부)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>

--- a/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
+++ b/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
@@ -49,7 +49,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'양식목록'!$8:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'양식목록'!$A$1:$F$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'문서관리'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'문서관리'!$A$1:$E$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'작성안내'!$A$1:$B$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PF-00'!$A$1:$G$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'QF-02'!$A$1:$G$29</definedName>
@@ -8851,7 +8851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E29"/>
+  <dimension ref="A2:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -8947,28 +8947,12 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="82.95" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>00 (보완)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2026.10.12</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>법정·인증 필수 정리: SF-04에 관리감독자 지정·반기 평가, MF-05에 관리감독자·휴게시설·법정 의무교육·인원 기준, SF-05에 성희롱 예방·장애인 인식개선 교육, QF-13 외부 문서 추가 / 근로자 협의·표본 복구 분기, 목표 실적·법규 최신성·예산 집행 확인 반기(SF-08 때)로 조정</t>
-        </is>
-      </c>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>대표 승인 후 적용</t>
-        </is>
-      </c>
+      <c r="E9" s="5" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5" t="n"/>
@@ -8977,37 +8961,41 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="10" customHeight="1"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="11" ht="10" customHeight="1"/>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>시행 전 확인 항목 (매뉴얼 부록 D)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>확인 결과</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>확인자·일자</t>
         </is>
       </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>1. 인증 범위·적용 규격 판본, 2026판 전환 계획 (MF-05)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1. 인증 범위·적용 규격 판본, 2026판 전환 계획 (MF-05)</t>
+          <t>2. 고객별 요구·최신 점검표 판본 (QF-14·MF-05)</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -9018,7 +9006,7 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2. 고객별 요구·최신 점검표 판본 (QF-14·MF-05)</t>
+          <t>3. 안전·환경 법규 적용 여부와 기록 보존기간 (MF-05)</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -9029,7 +9017,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3. 안전·환경 법규 적용 여부와 기록 보존기간 (MF-05)</t>
+          <t>4. 공용 저장소 실제 경로·접근권한·분리 백업·복구 확인 (QF-13·QF-13-2)</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -9040,7 +9028,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4. 공용 저장소 실제 경로·접근권한·분리 백업·복구 확인 (QF-13·QF-13-2)</t>
+          <t>5. 안전보건관리담당자 선임 또는 위탁 증빙 (SF-04)</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -9051,7 +9039,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>5. 안전보건관리담당자 선임 또는 위탁 증빙 (SF-04)</t>
+          <t>6. 연간 교육 계획·건강진단 대상·안전보건 예산 (SF-05·SF-06·SF-07)</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -9062,7 +9050,7 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>6. 연간 교육 계획·건강진단 대상·안전보건 예산 (SF-05·SF-06·SF-07)</t>
+          <t>7. 최초 위험성평가 일정 — 시행일부터 1개월 이내 (SF-01)</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -9073,7 +9061,7 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>7. 최초 위험성평가 일정 — 시행일부터 1개월 이내 (SF-01)</t>
+          <t>8. QF-15 기술기준 승인 책임자, 작업·검사 자격 (QF-12)</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -9084,7 +9072,7 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>8. QF-15 기술기준 승인 책임자, 작업·검사 자격 (QF-12)</t>
+          <t>9. 내부심사원 독립성, 근로자 참여·비상훈련 준비 (MF-01·MF-06)</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -9095,7 +9083,7 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>9. 내부심사원 독립성, 근로자 참여·비상훈련 준비 (MF-01·MF-06)</t>
+          <t>10. 모든 양식 참조·인쇄 상태 확인, 담당자 교육</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -9106,7 +9094,7 @@
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>10. 모든 양식 참조·인쇄 상태 확인, 담당자 교육</t>
+          <t>11. 기존 초안·검토본 사용중지 표시, QF-13 배포 기록</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -9114,56 +9102,56 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="5" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>11. 기존 초안·검토본 사용중지 표시, QF-13 배포 기록</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>첨부·대체 기록 번호와 보관 경로 / 적용 제외(해당없음) 사유 / 미결 확인 :</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>작성(품질)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>검토(기술·안전·환경)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>승인(대표이사)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>성명·서명</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>성명·서명</t>
+          <t>일자</t>
         </is>
       </c>
       <c r="B28" s="9" t="n"/>
@@ -9171,41 +9159,30 @@
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D14:D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 확인, 미흡, 해당없음" type="list" errorStyle="warning">
+    <dataValidation sqref="D13:D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르십시오: 확인, 미흡, 해당없음" type="list" errorStyle="warning">
       <formula1>"확인,미흡,해당없음"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18915,12 +18892,12 @@
     <row r="33" ht="31.65" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>남녀고용평등법 제13조 · 장애인고용촉진법 제5조의2</t>
+          <t>고용보험법·산재보험법 (일용근로자)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>성희롱 예방교육·장애인 인식개선 교육 연 1회 (SF-05)</t>
+          <t>근로내용확인신고 — 일용직 쓴 달 다음 달 15일까지 (경영관리), 접수증 보관</t>
         </is>
       </c>
       <c r="C33" s="5" t="n"/>
@@ -18930,15 +18907,15 @@
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="5" t="n"/>
     </row>
-    <row r="34" ht="44.475" customHeight="1">
+    <row r="34" ht="31.65" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>인원 기준 변동 (상시 30명·50명)</t>
+          <t>남녀고용평등법 제13조 · 장애인고용촉진법 제5조의2</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>30명 이상 노사협의회 / 50명 이상 안전보건관리책임자·안전·보건관리자·산업안전보건위원회 — 인원 변동 시 재확인</t>
+          <t>성희롱 예방교육·장애인 인식개선 교육 연 1회 (SF-05)</t>
         </is>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -18948,9 +18925,17 @@
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="5" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
+    <row r="35" ht="44.475" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>인원 기준 변동 (상시 30명·50명)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>30명 이상 노사협의회 / 50명 이상 안전보건관리책임자·안전·보건관리자·산업안전보건위원회 — 인원 변동 시 재확인</t>
+        </is>
+      </c>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>

--- a/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
+++ b/_src/iso/source/DI-IMS-F-01_Rev00.xlsx
@@ -123,7 +123,7 @@
     <font>
       <name val="Malgun Gothic"/>
       <b val="1"/>
-      <color rgb="001857A5"/>
+      <color rgb="000A2A55"/>
       <sz val="16"/>
     </font>
     <font>
@@ -175,7 +175,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001857A5"/>
+        <fgColor rgb="000A2A55"/>
       </patternFill>
     </fill>
     <fill>
@@ -11730,12 +11730,12 @@
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>작업허가·현장규칙</t>
         </is>
       </c>
+      <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
@@ -11979,12 +11979,11 @@
       <c r="F25" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A23:B25"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A8:B8"/>
